--- a/src/main/resources/account/default/BAS-2026---Handelsbolag-och-kommanditbolag.xlsx
+++ b/src/main/resources/account/default/BAS-2026---Handelsbolag-och-kommanditbolag.xlsx
@@ -427,6 +427,9 @@
           <t>BAS 2026 - Handelsbolag och kommanditbolag</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +442,9 @@
           <t>EUBAS97</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +457,9 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,6 +470,9 @@
       <c r="B4" t="n">
         <v>6</v>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2776,7 +2788,11 @@
           <t>Pågående arbeten, nedlagda kostnader</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>7245</t>
@@ -6413,7 +6429,11 @@
           <t>Kortfristiga lån från kreditinstitut</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D361" t="inlineStr">
         <is>
           <t>7371</t>
@@ -6430,7 +6450,11 @@
           <t>Byggnadskreditiv, kortfristig del</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
           <t>7371</t>
@@ -6498,7 +6522,11 @@
           <t>Ej inlösta presentkort</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D366" t="inlineStr">
         <is>
           <t>7362</t>
@@ -6549,7 +6577,11 @@
           <t>Pågående arbeten, fakturering</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D369" t="inlineStr">
         <is>
           <t>7363</t>
@@ -7042,7 +7074,11 @@
           <t>Utgående moms, 25 %</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D398" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7059,7 +7095,11 @@
           <t>Utgående moms på försäljning inom Sverige, 25 %</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7076,7 +7116,11 @@
           <t>Utgående moms på egna uttag, 25 %</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D400" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7093,7 +7137,11 @@
           <t>Utgående moms för uthyrning, 25 %</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D401" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7110,7 +7158,11 @@
           <t>Utgående moms omvänd betalskyldighet, 25 %</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>U1MI</t>
+        </is>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7127,7 +7179,11 @@
           <t>Utgående moms import av varor, 25 %</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>U1MI</t>
+        </is>
+      </c>
       <c r="D403" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7161,7 +7217,11 @@
           <t>Vilande utgående moms, 25 %</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D405" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7195,7 +7255,11 @@
           <t>Utgående moms på försäljning inom Sverige, 12 %</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D407" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7212,7 +7276,11 @@
           <t>Utgående moms på egna uttag, 12 %</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D408" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7246,7 +7314,11 @@
           <t>Utgående moms omvänd betalningsskyldighet 12 %</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>U2MI</t>
+        </is>
+      </c>
       <c r="D410" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7263,7 +7335,11 @@
           <t>Utgående moms import av varor, 12 %</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>U2MI</t>
+        </is>
+      </c>
       <c r="D411" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7297,7 +7373,11 @@
           <t>Vilande utgående moms, 12 %</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D413" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7331,7 +7411,11 @@
           <t>Utgående moms på försäljning inom Sverige, 6 %</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D415" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7348,7 +7432,11 @@
           <t>Utgående moms på egna uttag, 6 %</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7382,7 +7470,11 @@
           <t>Utgående moms omvänd betalningsskyldighet, 6 %</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>U3MI</t>
+        </is>
+      </c>
       <c r="D418" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7399,7 +7491,11 @@
           <t>Utgående moms import av varor, 6 %</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>U3MI</t>
+        </is>
+      </c>
       <c r="D419" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7433,7 +7529,11 @@
           <t>Vilande utgående moms, 6 %</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D421" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7450,7 +7550,11 @@
           <t>Ingående moms</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D422" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7467,7 +7571,11 @@
           <t>Debiterad ingående moms</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D423" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7484,7 +7592,11 @@
           <t>Debiterad ingående moms i anslutning till frivillig betalningsskyldighet</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D424" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7501,7 +7613,11 @@
           <t>Beräknad ingående moms på förvärv från utlandet</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D425" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7518,7 +7634,11 @@
           <t>Ingående moms på uthyrning</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D426" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7552,7 +7672,11 @@
           <t>Vilande ingående moms</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D428" t="inlineStr">
         <is>
           <t>7371</t>
@@ -7569,7 +7693,11 @@
           <t>Ingående moms, blandad verksamhet</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D429" t="inlineStr">
         <is>
           <t>7371</t>
@@ -9289,7 +9417,11 @@
           <t>Fakturerade kostnader (gruppkonto)</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr"/>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D529" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9306,7 +9438,11 @@
           <t>Fakturerat emballage</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr"/>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D530" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9357,7 +9493,11 @@
           <t>Fakturerade frakter</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D533" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9391,7 +9531,11 @@
           <t>Fakturerade frakter, export</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr"/>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>VTEU</t>
+        </is>
+      </c>
       <c r="D535" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9408,7 +9552,11 @@
           <t>Fakturerade tull- och  speditionskostnader m.m.</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr"/>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="D536" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9425,7 +9573,11 @@
           <t>Faktureringsavgifter</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr"/>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D537" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9442,7 +9594,11 @@
           <t>Faktureringsavgifter, EU-land</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="D538" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9459,7 +9615,11 @@
           <t>Faktureringsavgifter, export</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr"/>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>VTEU</t>
+        </is>
+      </c>
       <c r="D539" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9476,7 +9636,11 @@
           <t>Fakturerade resekostnader</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr"/>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D540" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9493,7 +9657,11 @@
           <t>Fakturerade kostnader till  koncernföretag</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr"/>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D541" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9561,7 +9729,11 @@
           <t>Fakturerade kostnader till  intresseföretag, gemensamt styrda företag och övriga företag som det finns ett ägarintresse i</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D545" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9578,7 +9750,11 @@
           <t>Övriga fakturerade kostnader</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D546" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9595,7 +9771,11 @@
           <t>Rörelsens sidointäkter (gruppkonto)</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D547" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9612,7 +9792,11 @@
           <t>Försäljning av material</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D548" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9697,7 +9881,11 @@
           <t>Tillfällig uthyrning av personal</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D553" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9816,7 +10004,11 @@
           <t>Övriga sidointäkter</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr"/>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D560" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9833,7 +10025,11 @@
           <t>Intäktskorrigeringar (gruppkonto)</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D561" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9850,7 +10046,11 @@
           <t>Ofördelade intäktsreduktioner</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr"/>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D562" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9867,7 +10067,11 @@
           <t>Lämnade rabatter</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D563" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9939,7 +10143,11 @@
           <t>Punktskatter</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr"/>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D567" t="inlineStr">
         <is>
           <t>7410</t>
@@ -9990,7 +10198,11 @@
           <t>Övriga intäktskorrigeringar</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D570" t="inlineStr">
         <is>
           <t>7410</t>
@@ -10041,7 +10253,11 @@
           <t>Aktiverat arbete (omkostnader)</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D573" t="inlineStr">
         <is>
           <t>7412</t>
@@ -10075,7 +10291,11 @@
           <t>Övriga rörelseintäkter (gruppkonto)</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D575" t="inlineStr">
         <is>
           <t>7413</t>
@@ -10262,7 +10482,11 @@
           <t>Återvunna, tidigare avskrivna  kundfordringar</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D586" t="inlineStr">
         <is>
           <t>7413</t>
@@ -10364,7 +10588,11 @@
           <t>Erhållna offentliga bidrag</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr"/>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D592" t="inlineStr">
         <is>
           <t>7413</t>
@@ -10466,7 +10694,11 @@
           <t>Övriga ersättningar, bidrag och  intäkter</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D598" t="inlineStr">
         <is>
           <t>7413</t>
